--- a/artfynd/A 28636-2026 artfynd.xlsx
+++ b/artfynd/A 28636-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78481540</v>
+        <v>134665307</v>
       </c>
       <c r="B2" t="n">
-        <v>99456</v>
+        <v>79130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skarpen, Hls</t>
+          <t>Finneby, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527242</v>
+        <v>527154</v>
       </c>
       <c r="R2" t="n">
-        <v>6881706</v>
+        <v>6881657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lite</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,15 +769,223 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>78481540</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skarpen, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>527242</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6881706</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lite</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Tony Svensson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Tony Svensson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134665308</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Finneby, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>527154</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6881657</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28636-2026 artfynd.xlsx
+++ b/artfynd/A 28636-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665307</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78481540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,8 +1001,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665308</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>